--- a/Материалы/DBD/Ключи кружки.xlsx
+++ b/Материалы/DBD/Ключи кружки.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -170,13 +170,13 @@
     <t>DBD Призрак</t>
   </si>
   <si>
-    <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Призрак, Wraith, Неа Карлссон, Nea Karlsson</t>
+    <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Призрак, Wraith, Елвин, Eleven</t>
   </si>
   <si>
     <t>DBD Охотник</t>
   </si>
   <si>
-    <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Охотник, Ловец, Trapper, Траппер, Дэвид Кинг, David King</t>
+    <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Охотник, Ловец, Trapper, Траппер, Нэнси Уилер, Nancy Wheeler</t>
   </si>
 </sst>
 </file>
@@ -1171,9 +1171,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="71.712962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="71.7142857142857" style="1" customWidth="1"/>
     <col min="2" max="2" width="130" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1289,7 +1289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:2">
+    <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>

--- a/Материалы/DBD/Ключи кружки.xlsx
+++ b/Материалы/DBD/Ключи кружки.xlsx
@@ -189,10 +189,17 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -202,6 +209,18 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -719,180 +738,185 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1173,529 +1197,529 @@
   <dimension ref="A1:B105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="71.7142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="71.7142857142857" style="2" customWidth="1"/>
     <col min="2" max="2" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:2">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:2">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:2">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:2">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:2">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
+    <row r="18" s="1" customFormat="1" spans="1:2">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:2">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:2">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+    <row r="21" s="1" customFormat="1" spans="1:2">
+      <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:2">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="9"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="9"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="9"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="6"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="9"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="6"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="9"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="9"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="9"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="7"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="10"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="5"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="10"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="10"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="7"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="10"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="7"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="10"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="10"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="8"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="10"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
+      <c r="A46" s="11"/>
+      <c r="B46" s="12"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="12"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="8"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="10"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="10"/>
-      <c r="B49" s="7"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="10"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="10"/>
-      <c r="B50" s="7"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="10"/>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="10"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="10"/>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="8"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="10"/>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="10"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="10"/>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="8"/>
-      <c r="B54" s="7"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="10"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="10"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="8"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="10"/>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="8"/>
-      <c r="B57" s="7"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="10"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="10"/>
-      <c r="B58" s="7"/>
+      <c r="A58" s="13"/>
+      <c r="B58" s="10"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="8"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="10"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="8"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="14"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="13"/>
+      <c r="B61" s="14"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="8"/>
-      <c r="B62" s="12"/>
+      <c r="A62" s="11"/>
+      <c r="B62" s="15"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="10"/>
-      <c r="B63" s="13"/>
+      <c r="A63" s="13"/>
+      <c r="B63" s="16"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="8"/>
-      <c r="B64" s="13"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="16"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="8"/>
-      <c r="B65" s="13"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="16"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="10"/>
-      <c r="B66" s="13"/>
+      <c r="A66" s="13"/>
+      <c r="B66" s="16"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="8"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="16"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="8"/>
-      <c r="B68" s="14"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="17"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="8"/>
-      <c r="B69" s="15"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="18"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="8"/>
-      <c r="B70" s="16"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="19"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="8"/>
-      <c r="B71" s="17"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="20"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="8"/>
-      <c r="B72" s="17"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="20"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="8"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="8"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="8"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="8"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="8"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="9"/>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="9"/>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="6"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="9"/>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="6"/>
+      <c r="A82" s="7"/>
+      <c r="B82" s="9"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="5"/>
-      <c r="B83" s="6"/>
+      <c r="A83" s="8"/>
+      <c r="B83" s="9"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="6"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="9"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="10"/>
-      <c r="B85" s="7"/>
+      <c r="A85" s="13"/>
+      <c r="B85" s="10"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="8"/>
-      <c r="B86" s="7"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="10"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="8"/>
-      <c r="B87" s="7"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="10"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="8"/>
-      <c r="B88" s="7"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="10"/>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="8"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="10"/>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="8"/>
-      <c r="B90" s="7"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="10"/>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="8"/>
-      <c r="B91" s="7"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="10"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="8"/>
-      <c r="B92" s="7"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="10"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
+      <c r="A93" s="8"/>
+      <c r="B93" s="9"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="9"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="4"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="9"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="4"/>
-      <c r="B96" s="7"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="10"/>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="4"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="10"/>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="7"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="10"/>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="4"/>
-      <c r="B99" s="7"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="10"/>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2"/>
-      <c r="B100" s="18"/>
+      <c r="A100" s="5"/>
+      <c r="B100" s="21"/>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2"/>
-      <c r="B101" s="18"/>
+      <c r="A101" s="5"/>
+      <c r="B101" s="21"/>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2"/>
-      <c r="B102" s="18"/>
+      <c r="A102" s="5"/>
+      <c r="B102" s="21"/>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2"/>
-      <c r="B103" s="18"/>
+      <c r="A103" s="5"/>
+      <c r="B103" s="21"/>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2"/>
-      <c r="B104" s="18"/>
+      <c r="A104" s="5"/>
+      <c r="B104" s="21"/>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="2"/>
-      <c r="B105" s="18"/>
+      <c r="A105" s="5"/>
+      <c r="B105" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Материалы/DBD/Ключи кружки.xlsx
+++ b/Материалы/DBD/Ключи кружки.xlsx
@@ -868,8 +868,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1197,529 +1198,529 @@
   <dimension ref="A1:B105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="71.7142857142857" style="2" customWidth="1"/>
+    <col min="1" max="1" width="71.7142857142857" style="3" customWidth="1"/>
     <col min="2" max="2" width="130" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="5" t="s">
+    <row r="12" s="2" customFormat="1" spans="1:2">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
+    <row r="22" s="2" customFormat="1" spans="1:2">
+      <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="5" t="s">
+    <row r="25" s="2" customFormat="1" spans="1:2">
+      <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="10"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="7"/>
-      <c r="B32" s="9"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="10"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="7"/>
-      <c r="B33" s="9"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="10"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="7"/>
-      <c r="B34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="10"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="7"/>
-      <c r="B35" s="9"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="9"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="10"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="9"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="10"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="10"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="11"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="8"/>
-      <c r="B39" s="10"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="11"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="7"/>
-      <c r="B40" s="10"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="11"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="7"/>
-      <c r="B41" s="10"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="11"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="7"/>
-      <c r="B42" s="10"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="11"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="7"/>
-      <c r="B43" s="10"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="11"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="11"/>
-      <c r="B44" s="10"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="11"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="11"/>
-      <c r="B48" s="10"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="11"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="13"/>
-      <c r="B49" s="10"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="11"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="13"/>
-      <c r="B50" s="10"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="11"/>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="10"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="11"/>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="10"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="11"/>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="13"/>
-      <c r="B53" s="10"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="11"/>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="10"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="11"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="10"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="11"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="10"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="11"/>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="11"/>
-      <c r="B57" s="10"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="11"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="13"/>
-      <c r="B58" s="10"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="11"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="11"/>
-      <c r="B59" s="10"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="11"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="11"/>
-      <c r="B60" s="14"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="15"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="15"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="15"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="16"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="13"/>
-      <c r="B63" s="16"/>
+      <c r="A63" s="14"/>
+      <c r="B63" s="17"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="11"/>
-      <c r="B64" s="16"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="17"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="11"/>
-      <c r="B65" s="16"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="17"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="13"/>
-      <c r="B66" s="16"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="17"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="11"/>
-      <c r="B67" s="16"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="17"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="11"/>
-      <c r="B68" s="17"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="18"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="11"/>
-      <c r="B69" s="18"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="19"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="19"/>
+      <c r="A70" s="12"/>
+      <c r="B70" s="20"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="20"/>
+      <c r="A71" s="12"/>
+      <c r="B71" s="21"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="11"/>
-      <c r="B72" s="20"/>
+      <c r="A72" s="12"/>
+      <c r="B72" s="21"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="7"/>
-      <c r="B74" s="8"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="9"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="7"/>
-      <c r="B76" s="8"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="9"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="7"/>
-      <c r="B77" s="8"/>
+      <c r="A77" s="8"/>
+      <c r="B77" s="9"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="7"/>
-      <c r="B78" s="8"/>
+      <c r="A78" s="8"/>
+      <c r="B78" s="9"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="10"/>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="7"/>
-      <c r="B80" s="9"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="7"/>
-      <c r="B81" s="9"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="10"/>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="7"/>
-      <c r="B82" s="9"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="10"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="10"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="7"/>
-      <c r="B84" s="9"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="10"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="13"/>
-      <c r="B85" s="10"/>
+      <c r="A85" s="14"/>
+      <c r="B85" s="11"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="11"/>
-      <c r="B86" s="10"/>
+      <c r="A86" s="12"/>
+      <c r="B86" s="11"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="11"/>
-      <c r="B87" s="10"/>
+      <c r="A87" s="12"/>
+      <c r="B87" s="11"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="11"/>
-      <c r="B88" s="10"/>
+      <c r="A88" s="12"/>
+      <c r="B88" s="11"/>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="11"/>
-      <c r="B89" s="10"/>
+      <c r="A89" s="12"/>
+      <c r="B89" s="11"/>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="11"/>
-      <c r="B90" s="10"/>
+      <c r="A90" s="12"/>
+      <c r="B90" s="11"/>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="11"/>
-      <c r="B91" s="10"/>
+      <c r="A91" s="12"/>
+      <c r="B91" s="11"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="11"/>
-      <c r="B92" s="10"/>
+      <c r="A92" s="12"/>
+      <c r="B92" s="11"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="10"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="7"/>
-      <c r="B94" s="9"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="10"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="7"/>
-      <c r="B95" s="9"/>
+      <c r="A95" s="8"/>
+      <c r="B95" s="10"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="7"/>
-      <c r="B96" s="10"/>
+      <c r="A96" s="8"/>
+      <c r="B96" s="11"/>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="7"/>
-      <c r="B97" s="10"/>
+      <c r="A97" s="8"/>
+      <c r="B97" s="11"/>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="7"/>
-      <c r="B98" s="10"/>
+      <c r="A98" s="8"/>
+      <c r="B98" s="11"/>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="7"/>
-      <c r="B99" s="10"/>
+      <c r="A99" s="8"/>
+      <c r="B99" s="11"/>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="5"/>
-      <c r="B100" s="21"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="22"/>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="5"/>
-      <c r="B101" s="21"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="22"/>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="5"/>
-      <c r="B102" s="21"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="22"/>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="5"/>
-      <c r="B103" s="21"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="22"/>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="5"/>
-      <c r="B104" s="21"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="22"/>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="5"/>
-      <c r="B105" s="21"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Материалы/DBD/Ключи кружки.xlsx
+++ b/Материалы/DBD/Ключи кружки.xlsx
@@ -41,7 +41,7 @@
     <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Выкованная в тумане, Рыцарь, Витторио Тоскано, Vittorio Toscano, Knight, Forged in Fog</t>
   </si>
   <si>
-    <t>266 CupDBDGam266.PQTC.22.03.26 DBD Resident Evil: PROJECT W</t>
+    <t>266 CupDBDGam266.PQTC.22.03.26 DBD Resident Evil_PROJECT W</t>
   </si>
   <si>
     <t>ДБД, DBD, Dead By daylight, игра, games, Маньяки из DBD, Маньяки из ДБД, Обитель зла: ПРОЕКТ W, Resident Evil: PROJECT W, Вдохновитель, Ада Вонг, Mastermind, Ada Wong</t>
@@ -189,7 +189,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,11 +219,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
       <charset val="204"/>
     </font>
@@ -738,137 +733,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -877,52 +872,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1242,55 +1234,55 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="6" t="s">
+    <row r="6" s="2" customFormat="1" spans="1:2">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="6" t="s">
+    <row r="7" s="2" customFormat="1" spans="1:2">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="6" t="s">
+    <row r="8" s="2" customFormat="1" spans="1:2">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="6" t="s">
+    <row r="9" s="2" customFormat="1" spans="1:2">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="6" t="s">
+    <row r="10" s="2" customFormat="1" spans="1:2">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6" t="s">
+    <row r="11" s="2" customFormat="1" spans="1:2">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:2">
+    <row r="12" s="1" customFormat="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -1306,19 +1298,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6" t="s">
+    <row r="14" s="2" customFormat="1" spans="1:2">
+      <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:2">
-      <c r="A15" s="6" t="s">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:2">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1330,11 +1322,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="6" t="s">
+    <row r="17" s="2" customFormat="1" spans="1:2">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1370,7 +1362,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:2">
+    <row r="22" s="1" customFormat="1" spans="1:2">
       <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
@@ -1386,15 +1378,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="6" t="s">
+    <row r="24" s="2" customFormat="1" spans="1:2">
+      <c r="A24" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:2">
+    <row r="25" s="1" customFormat="1" spans="1:2">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -1403,324 +1395,324 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="7"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="7"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="8"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="10"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="8"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="10"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="8"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="10"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="8"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="10"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="8"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="10"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="8"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="8"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="9"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="9"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="8"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="9"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="11"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="9"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="8"/>
-      <c r="B42" s="11"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="9"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="8"/>
-      <c r="B43" s="11"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="9"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="9"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="12"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="9"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="14"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="9"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="14"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="9"/>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="14"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="9"/>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="12"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="9"/>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="14"/>
-      <c r="B53" s="11"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="9"/>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="12"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="9"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="12"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="9"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="12"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="9"/>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="12"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="9"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="14"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="9"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="12"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="9"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="12"/>
-      <c r="B60" s="15"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="13"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="14"/>
-      <c r="B61" s="15"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="12"/>
-      <c r="B62" s="16"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="14"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="14"/>
-      <c r="B63" s="17"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="15"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="12"/>
-      <c r="B64" s="17"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="15"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="12"/>
-      <c r="B65" s="17"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="15"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="17"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="15"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="12"/>
-      <c r="B67" s="17"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="15"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="12"/>
-      <c r="B68" s="18"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="16"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="12"/>
-      <c r="B69" s="19"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="17"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="12"/>
-      <c r="B70" s="20"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="18"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="12"/>
-      <c r="B71" s="21"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="19"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="12"/>
-      <c r="B72" s="21"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="19"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="7"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="7"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
+      <c r="A77" s="6"/>
+      <c r="B77" s="7"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="7"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="9"/>
-      <c r="B79" s="10"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="8"/>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="8"/>
-      <c r="B80" s="10"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="8"/>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="8"/>
-      <c r="B81" s="10"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="8"/>
-      <c r="B82" s="10"/>
+      <c r="A82" s="6"/>
+      <c r="B82" s="8"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="9"/>
-      <c r="B83" s="10"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="8"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="8"/>
-      <c r="B84" s="10"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="8"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="14"/>
-      <c r="B85" s="11"/>
+      <c r="A85" s="12"/>
+      <c r="B85" s="9"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="12"/>
-      <c r="B86" s="11"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="9"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="12"/>
-      <c r="B87" s="11"/>
+      <c r="A87" s="10"/>
+      <c r="B87" s="9"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="12"/>
-      <c r="B88" s="11"/>
+      <c r="A88" s="10"/>
+      <c r="B88" s="9"/>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="12"/>
-      <c r="B89" s="11"/>
+      <c r="A89" s="10"/>
+      <c r="B89" s="9"/>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="12"/>
-      <c r="B90" s="11"/>
+      <c r="A90" s="10"/>
+      <c r="B90" s="9"/>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="12"/>
-      <c r="B91" s="11"/>
+      <c r="A91" s="10"/>
+      <c r="B91" s="9"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="12"/>
-      <c r="B92" s="11"/>
+      <c r="A92" s="10"/>
+      <c r="B92" s="9"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="9"/>
-      <c r="B93" s="10"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="8"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="8"/>
-      <c r="B94" s="10"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="8"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="8"/>
-      <c r="B95" s="10"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="8"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="8"/>
-      <c r="B96" s="11"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="9"/>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="8"/>
-      <c r="B97" s="11"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="8"/>
-      <c r="B98" s="11"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="9"/>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="8"/>
-      <c r="B99" s="11"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="6"/>
-      <c r="B100" s="22"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="21"/>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="6"/>
-      <c r="B101" s="22"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="21"/>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="6"/>
-      <c r="B102" s="22"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="21"/>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="6"/>
-      <c r="B103" s="22"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="21"/>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="6"/>
-      <c r="B104" s="22"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="21"/>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="6"/>
-      <c r="B105" s="22"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
